--- a/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -112,13 +112,10 @@
     <t>Operation</t>
   </si>
   <si>
-    <t>ror</t>
+    <t>finess</t>
   </si>
   <si>
     <t>=</t>
-  </si>
-  <si>
-    <t>true</t>
   </si>
 </sst>
 </file>
@@ -440,7 +437,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">

--- a/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
@@ -8,13 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Exclude #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>Property</t>
   </si>
@@ -94,10 +93,13 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
   <si>
     <t/>
@@ -107,15 +109,6 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R66-CategorieEtablissement/FHIR/TRE-R66-CategorieEtablissement</t>
-  </si>
-  <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>finess</t>
-  </si>
-  <si>
-    <t>=</t>
   </si>
 </sst>
 </file>
@@ -371,46 +364,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -423,7 +376,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -431,29 +384,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -96,10 +96,13 @@
     <t>Operation</t>
   </si>
   <si>
-    <t>=</t>
-  </si>
-  <si>
-    <t>true</t>
+    <t>code</t>
+  </si>
+  <si>
+    <t>regex</t>
+  </si>
+  <si>
+    <t>^([0-6][0-9]{2})$</t>
   </si>
   <si>
     <t/>
@@ -384,29 +387,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
@@ -111,7 +111,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R66-CategorieEtablissement/FHIR/TRE-R66-CategorieEtablissement</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r397-categorie-entite-geographique-exercice</t>
   </si>
 </sst>
 </file>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Exclude #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -96,13 +97,13 @@
     <t>Operation</t>
   </si>
   <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>regex</t>
-  </si>
-  <si>
-    <t>^([0-6][0-9]{2})$</t>
+    <t>niveau</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t/>
@@ -112,6 +113,12 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r397-categorie-entite-geographique-exercice</t>
+  </si>
+  <si>
+    <t>specialisationRor</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
 </sst>
 </file>
@@ -415,4 +422,56 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Jeu de valeurs FINESS contenant les catégories d'entité géographique d'exercice spécifiques à FINESS</t>
+    <t>Jeu de valeurs FINESS contenant les catégories d'entité géographique d'exercice spécifiques à FINESS et de niveau 4</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250611120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T18:02:28.249+00:00</t>
+    <t>2026-02-23T12:00:00.000+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Jeu de valeurs FINESS contenant les catégories d'entité géographique d'exercice spécifiques à FINESS et de niveau 4</t>
+    <t>Ce JDV contient toutes les catégories d'EGE hors agrégat (JDV crée à l'image de l'ancienne TRE R66)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -252,7 +258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -351,20 +357,28 @@
       <c r="A12" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>25</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -386,7 +400,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -394,29 +408,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -438,7 +452,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -446,29 +460,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
